--- a/backtest_runs/20260410_193731/by_symbol/BUXL/BUXL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/BUXL/BUXL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -584,10 +584,10 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>103975.1</v>
@@ -633,7 +633,7 @@
         <v>-2529.039999999995</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>101446.06</v>
@@ -771,7 +771,7 @@
         <v>-1170.620000000003</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>100275.44</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>100275.44</v>
@@ -1139,7 +1139,7 @@
         <v>-4250.539999999995</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>101640.12</v>
@@ -1277,7 +1277,7 @@
         <v>-5220.840000000002</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>106184.88</v>
@@ -1553,7 +1553,7 @@
         <v>-1834.179999999986</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>104463.38</v>
